--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,922 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121515866</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594205</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7183737</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121515878</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594083</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7183653</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121515968</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594483</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7183422</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121515877</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97052</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>594085</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7183658</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121515969</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594483</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7183422</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121515967</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>594559</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7183360</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121515865</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>594203</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7183741</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121515879</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>594084</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7183645</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515878</v>
+        <v>121515968</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594083</v>
+        <v>594483</v>
       </c>
       <c r="R6" t="n">
-        <v>7183653</v>
+        <v>7183422</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515968</v>
+        <v>121515878</v>
       </c>
       <c r="B7" t="n">
         <v>57354</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594483</v>
+        <v>594083</v>
       </c>
       <c r="R7" t="n">
-        <v>7183422</v>
+        <v>7183653</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515877</v>
+        <v>121515967</v>
       </c>
       <c r="B8" t="n">
-        <v>97052</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,38 +1387,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594085</v>
+        <v>594559</v>
       </c>
       <c r="R8" t="n">
-        <v>7183658</v>
+        <v>7183360</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515969</v>
+        <v>121515865</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1508,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594483</v>
+        <v>594203</v>
       </c>
       <c r="R9" t="n">
-        <v>7183422</v>
+        <v>7183741</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515967</v>
+        <v>121515879</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,39 +1620,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594559</v>
+        <v>594084</v>
       </c>
       <c r="R10" t="n">
-        <v>7183360</v>
+        <v>7183645</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515865</v>
+        <v>121515969</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594203</v>
+        <v>594483</v>
       </c>
       <c r="R11" t="n">
-        <v>7183741</v>
+        <v>7183422</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515879</v>
+        <v>121515877</v>
       </c>
       <c r="B12" t="n">
-        <v>90731</v>
+        <v>97052</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,25 +1840,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594084</v>
+        <v>594085</v>
       </c>
       <c r="R12" t="n">
-        <v>7183645</v>
+        <v>7183658</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515866</v>
+        <v>121515878</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594205</v>
+        <v>594083</v>
       </c>
       <c r="R5" t="n">
-        <v>7183737</v>
+        <v>7183653</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515968</v>
+        <v>121515879</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,39 +1157,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594483</v>
+        <v>594084</v>
       </c>
       <c r="R6" t="n">
-        <v>7183422</v>
+        <v>7183645</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515878</v>
+        <v>121515877</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>97058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,43 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594083</v>
+        <v>594085</v>
       </c>
       <c r="R7" t="n">
-        <v>7183653</v>
+        <v>7183658</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515967</v>
+        <v>121515865</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,39 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594559</v>
+        <v>594203</v>
       </c>
       <c r="R8" t="n">
-        <v>7183360</v>
+        <v>7183741</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1455,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515865</v>
+        <v>121515866</v>
       </c>
       <c r="B9" t="n">
-        <v>90731</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,34 +1493,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594203</v>
+        <v>594205</v>
       </c>
       <c r="R9" t="n">
-        <v>7183741</v>
+        <v>7183737</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1604,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515879</v>
+        <v>121515968</v>
       </c>
       <c r="B10" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,34 +1610,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594084</v>
+        <v>594483</v>
       </c>
       <c r="R10" t="n">
-        <v>7183645</v>
+        <v>7183422</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1714,7 @@
         <v>121515969</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1828,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515877</v>
+        <v>121515967</v>
       </c>
       <c r="B12" t="n">
-        <v>97052</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,38 +1835,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594085</v>
+        <v>594559</v>
       </c>
       <c r="R12" t="n">
-        <v>7183658</v>
+        <v>7183360</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515878</v>
+        <v>121515877</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,43 +1036,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594083</v>
+        <v>594085</v>
       </c>
       <c r="R5" t="n">
-        <v>7183653</v>
+        <v>7183658</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515879</v>
+        <v>121515865</v>
       </c>
       <c r="B6" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594084</v>
+        <v>594203</v>
       </c>
       <c r="R6" t="n">
-        <v>7183645</v>
+        <v>7183741</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515877</v>
+        <v>121515969</v>
       </c>
       <c r="B7" t="n">
-        <v>97058</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1260,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594085</v>
+        <v>594483</v>
       </c>
       <c r="R7" t="n">
-        <v>7183658</v>
+        <v>7183422</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515865</v>
+        <v>121515878</v>
       </c>
       <c r="B8" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1376,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594203</v>
+        <v>594083</v>
       </c>
       <c r="R8" t="n">
-        <v>7183741</v>
+        <v>7183653</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515866</v>
+        <v>121515879</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,39 +1493,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594205</v>
+        <v>594084</v>
       </c>
       <c r="R9" t="n">
-        <v>7183737</v>
+        <v>7183645</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515968</v>
+        <v>121515866</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,16 +1605,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1630,7 +1625,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1639,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594483</v>
+        <v>594205</v>
       </c>
       <c r="R10" t="n">
-        <v>7183422</v>
+        <v>7183737</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515969</v>
+        <v>121515968</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,24 +1722,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1826,7 +1826,7 @@
         <v>121515967</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515877</v>
+        <v>121515968</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,38 +1036,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594085</v>
+        <v>594483</v>
       </c>
       <c r="R5" t="n">
-        <v>7183658</v>
+        <v>7183422</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515865</v>
+        <v>121515879</v>
       </c>
       <c r="B6" t="n">
         <v>90738</v>
@@ -1176,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594203</v>
+        <v>594084</v>
       </c>
       <c r="R6" t="n">
-        <v>7183741</v>
+        <v>7183645</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515969</v>
+        <v>121515877</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594483</v>
+        <v>594085</v>
       </c>
       <c r="R7" t="n">
-        <v>7183422</v>
+        <v>7183658</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515878</v>
+        <v>121515865</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,39 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594083</v>
+        <v>594203</v>
       </c>
       <c r="R8" t="n">
-        <v>7183653</v>
+        <v>7183741</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515879</v>
+        <v>121515866</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,34 +1493,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594084</v>
+        <v>594205</v>
       </c>
       <c r="R9" t="n">
-        <v>7183645</v>
+        <v>7183737</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1552,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515866</v>
+        <v>121515878</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,16 +1610,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1625,7 +1630,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1634,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594205</v>
+        <v>594083</v>
       </c>
       <c r="R10" t="n">
-        <v>7183737</v>
+        <v>7183653</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515968</v>
+        <v>121515967</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1742,7 +1747,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594483</v>
+        <v>594559</v>
       </c>
       <c r="R11" t="n">
-        <v>7183422</v>
+        <v>7183360</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515967</v>
+        <v>121515969</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,39 +1844,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594559</v>
+        <v>594483</v>
       </c>
       <c r="R12" t="n">
-        <v>7183360</v>
+        <v>7183422</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515968</v>
+        <v>121515879</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,39 +1040,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594483</v>
+        <v>594084</v>
       </c>
       <c r="R5" t="n">
-        <v>7183422</v>
+        <v>7183645</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515879</v>
+        <v>121515865</v>
       </c>
       <c r="B6" t="n">
         <v>90738</v>
@@ -1181,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594084</v>
+        <v>594203</v>
       </c>
       <c r="R6" t="n">
-        <v>7183645</v>
+        <v>7183741</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515877</v>
+        <v>121515968</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1260,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594085</v>
+        <v>594483</v>
       </c>
       <c r="R7" t="n">
-        <v>7183658</v>
+        <v>7183422</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515865</v>
+        <v>121515967</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1381,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594203</v>
+        <v>594559</v>
       </c>
       <c r="R8" t="n">
-        <v>7183741</v>
+        <v>7183360</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515866</v>
+        <v>121515877</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,43 +1494,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594205</v>
+        <v>594085</v>
       </c>
       <c r="R9" t="n">
-        <v>7183737</v>
+        <v>7183658</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515878</v>
+        <v>121515866</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594083</v>
+        <v>594205</v>
       </c>
       <c r="R10" t="n">
-        <v>7183653</v>
+        <v>7183737</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515967</v>
+        <v>121515878</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1747,7 +1747,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594559</v>
+        <v>594083</v>
       </c>
       <c r="R11" t="n">
-        <v>7183360</v>
+        <v>7183653</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515879</v>
+        <v>121515865</v>
       </c>
       <c r="B5" t="n">
         <v>90738</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594084</v>
+        <v>594203</v>
       </c>
       <c r="R5" t="n">
-        <v>7183645</v>
+        <v>7183741</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515865</v>
+        <v>121515967</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,34 +1152,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594203</v>
+        <v>594559</v>
       </c>
       <c r="R6" t="n">
-        <v>7183741</v>
+        <v>7183360</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515968</v>
+        <v>121515877</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,43 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594483</v>
+        <v>594085</v>
       </c>
       <c r="R7" t="n">
-        <v>7183422</v>
+        <v>7183658</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515967</v>
+        <v>121515969</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,39 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594559</v>
+        <v>594483</v>
       </c>
       <c r="R8" t="n">
-        <v>7183360</v>
+        <v>7183422</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1445,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515877</v>
+        <v>121515879</v>
       </c>
       <c r="B9" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,25 +1489,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594085</v>
+        <v>594084</v>
       </c>
       <c r="R9" t="n">
-        <v>7183658</v>
+        <v>7183645</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1828,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515969</v>
+        <v>121515968</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,24 +1839,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1589,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515866</v>
+        <v>121515878</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,16 +1605,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594205</v>
+        <v>594083</v>
       </c>
       <c r="R10" t="n">
-        <v>7183737</v>
+        <v>7183653</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515878</v>
+        <v>121515866</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594083</v>
+        <v>594205</v>
       </c>
       <c r="R11" t="n">
-        <v>7183653</v>
+        <v>7183737</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515967</v>
+        <v>121515866</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594559</v>
+        <v>594205</v>
       </c>
       <c r="R5" t="n">
-        <v>7183360</v>
+        <v>7183737</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515878</v>
+        <v>121515877</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,43 +1153,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594083</v>
+        <v>594085</v>
       </c>
       <c r="R6" t="n">
-        <v>7183653</v>
+        <v>7183658</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515865</v>
+        <v>121515969</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594203</v>
+        <v>594483</v>
       </c>
       <c r="R7" t="n">
-        <v>7183741</v>
+        <v>7183422</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515969</v>
+        <v>121515968</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,24 +1381,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515879</v>
+        <v>121515878</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,34 +1498,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594084</v>
+        <v>594083</v>
       </c>
       <c r="R9" t="n">
-        <v>7183645</v>
+        <v>7183653</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1594,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515877</v>
+        <v>121515879</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,25 +1611,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594085</v>
+        <v>594084</v>
       </c>
       <c r="R10" t="n">
-        <v>7183658</v>
+        <v>7183645</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515866</v>
+        <v>121515865</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1727,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594205</v>
+        <v>594203</v>
       </c>
       <c r="R11" t="n">
-        <v>7183737</v>
+        <v>7183741</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515968</v>
+        <v>121515967</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1859,7 +1859,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594483</v>
+        <v>594559</v>
       </c>
       <c r="R12" t="n">
-        <v>7183422</v>
+        <v>7183360</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515866</v>
+        <v>121515969</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,39 +1040,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594205</v>
+        <v>594483</v>
       </c>
       <c r="R5" t="n">
-        <v>7183737</v>
+        <v>7183422</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515877</v>
+        <v>121515879</v>
       </c>
       <c r="B6" t="n">
-        <v>97067</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594085</v>
+        <v>594084</v>
       </c>
       <c r="R6" t="n">
-        <v>7183658</v>
+        <v>7183645</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515969</v>
+        <v>121515866</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,34 +1264,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594483</v>
+        <v>594205</v>
       </c>
       <c r="R7" t="n">
-        <v>7183422</v>
+        <v>7183737</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515968</v>
+        <v>121515877</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,43 +1377,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594483</v>
+        <v>594085</v>
       </c>
       <c r="R8" t="n">
-        <v>7183422</v>
+        <v>7183658</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1445,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,7 +1594,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515879</v>
+        <v>121515865</v>
       </c>
       <c r="B10" t="n">
         <v>90746</v>
@@ -1639,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594084</v>
+        <v>594203</v>
       </c>
       <c r="R10" t="n">
-        <v>7183645</v>
+        <v>7183741</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515865</v>
+        <v>121515967</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,34 +1722,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594203</v>
+        <v>594559</v>
       </c>
       <c r="R11" t="n">
-        <v>7183741</v>
+        <v>7183360</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,7 +1823,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515967</v>
+        <v>121515968</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1859,7 +1859,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594559</v>
+        <v>594483</v>
       </c>
       <c r="R12" t="n">
-        <v>7183360</v>
+        <v>7183422</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515969</v>
+        <v>121515865</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594483</v>
+        <v>594203</v>
       </c>
       <c r="R5" t="n">
-        <v>7183422</v>
+        <v>7183741</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515879</v>
+        <v>121515866</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,34 +1152,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594084</v>
+        <v>594205</v>
       </c>
       <c r="R6" t="n">
-        <v>7183645</v>
+        <v>7183737</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515866</v>
+        <v>121515877</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,43 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594205</v>
+        <v>594085</v>
       </c>
       <c r="R7" t="n">
-        <v>7183737</v>
+        <v>7183658</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515877</v>
+        <v>121515879</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594085</v>
+        <v>594084</v>
       </c>
       <c r="R8" t="n">
-        <v>7183658</v>
+        <v>7183645</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515878</v>
+        <v>121515968</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594083</v>
+        <v>594483</v>
       </c>
       <c r="R9" t="n">
-        <v>7183653</v>
+        <v>7183422</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515865</v>
+        <v>121515967</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,34 +1610,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594203</v>
+        <v>594559</v>
       </c>
       <c r="R10" t="n">
-        <v>7183741</v>
+        <v>7183360</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515967</v>
+        <v>121515878</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1742,7 +1747,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594559</v>
+        <v>594083</v>
       </c>
       <c r="R11" t="n">
-        <v>7183360</v>
+        <v>7183653</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515968</v>
+        <v>121515969</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,29 +1844,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515865</v>
+        <v>121515969</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594203</v>
+        <v>594483</v>
       </c>
       <c r="R5" t="n">
-        <v>7183741</v>
+        <v>7183422</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515866</v>
+        <v>121515968</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594205</v>
+        <v>594483</v>
       </c>
       <c r="R6" t="n">
-        <v>7183737</v>
+        <v>7183422</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515877</v>
+        <v>121515879</v>
       </c>
       <c r="B7" t="n">
-        <v>97067</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594085</v>
+        <v>594084</v>
       </c>
       <c r="R7" t="n">
-        <v>7183658</v>
+        <v>7183645</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515879</v>
+        <v>121515865</v>
       </c>
       <c r="B8" t="n">
         <v>90746</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594084</v>
+        <v>594203</v>
       </c>
       <c r="R8" t="n">
-        <v>7183645</v>
+        <v>7183741</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515968</v>
+        <v>121515878</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594483</v>
+        <v>594083</v>
       </c>
       <c r="R9" t="n">
-        <v>7183422</v>
+        <v>7183653</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515967</v>
+        <v>121515877</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,43 +1606,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594559</v>
+        <v>594085</v>
       </c>
       <c r="R10" t="n">
-        <v>7183360</v>
+        <v>7183658</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1706,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515878</v>
+        <v>121515967</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1747,7 +1742,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1756,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594083</v>
+        <v>594559</v>
       </c>
       <c r="R11" t="n">
-        <v>7183653</v>
+        <v>7183360</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1791,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515969</v>
+        <v>121515866</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,34 +1839,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594483</v>
+        <v>594205</v>
       </c>
       <c r="R12" t="n">
-        <v>7183422</v>
+        <v>7183737</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 32456-2024 artfynd.xlsx
+++ b/artfynd/A 32456-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515969</v>
+        <v>121515967</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,34 +1040,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594483</v>
+        <v>594559</v>
       </c>
       <c r="R5" t="n">
-        <v>7183422</v>
+        <v>7183360</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1253,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515879</v>
+        <v>121515877</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1270,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594084</v>
+        <v>594085</v>
       </c>
       <c r="R7" t="n">
-        <v>7183645</v>
+        <v>7183658</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515865</v>
+        <v>121515866</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1386,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594203</v>
+        <v>594205</v>
       </c>
       <c r="R8" t="n">
-        <v>7183741</v>
+        <v>7183737</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1477,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515878</v>
+        <v>121515879</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,39 +1503,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594083</v>
+        <v>594084</v>
       </c>
       <c r="R9" t="n">
-        <v>7183653</v>
+        <v>7183645</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1594,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515877</v>
+        <v>121515969</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,25 +1611,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594085</v>
+        <v>594483</v>
       </c>
       <c r="R10" t="n">
-        <v>7183658</v>
+        <v>7183422</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515967</v>
+        <v>121515865</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1727,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594559</v>
+        <v>594203</v>
       </c>
       <c r="R11" t="n">
-        <v>7183360</v>
+        <v>7183741</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515866</v>
+        <v>121515878</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,16 +1839,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1859,7 +1859,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594205</v>
+        <v>594083</v>
       </c>
       <c r="R12" t="n">
-        <v>7183737</v>
+        <v>7183653</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
